--- a/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_drugs_biotechnology.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-18.7</v>
+        <v>-13.5</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,31 +612,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>27.3</v>
+        <v>15</v>
       </c>
       <c r="V2">
-        <v>0.1906424581005587</v>
+        <v>0.1661129568106312</v>
       </c>
       <c r="W2">
-        <v>-0.1829745596868884</v>
+        <v>-0.1062155782848151</v>
       </c>
       <c r="X2">
-        <v>0.1343347019657854</v>
+        <v>0.2534166811357051</v>
       </c>
       <c r="Y2">
-        <v>-0.3173092616526738</v>
+        <v>-0.3596322594205202</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.3012598137666606</v>
+        <v>-0.2761061946902655</v>
       </c>
       <c r="AB2">
-        <v>0.1343347019657854</v>
+        <v>0.2534166811357051</v>
       </c>
       <c r="AC2">
-        <v>-0.435594515732446</v>
+        <v>-0.5295228758259707</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-27.3</v>
+        <v>-15</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -657,22 +657,22 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.2355478861087144</v>
+        <v>-0.199203187250996</v>
       </c>
       <c r="AK2">
-        <v>-0.1866028708133972</v>
+        <v>-0.09213759213759214</v>
       </c>
       <c r="AL2">
-        <v>0.049</v>
+        <v>0.011</v>
       </c>
       <c r="AM2">
-        <v>0.049</v>
+        <v>-0.05400000000000001</v>
       </c>
       <c r="AO2">
-        <v>-336.734693877551</v>
+        <v>-1418.181818181818</v>
       </c>
       <c r="AQ2">
-        <v>-336.734693877551</v>
+        <v>288.8888888888889</v>
       </c>
     </row>
     <row r="3">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-18.7</v>
+        <v>-13.5</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -716,31 +716,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>27.3</v>
+        <v>15</v>
       </c>
       <c r="V3">
-        <v>0.1906424581005587</v>
+        <v>0.1661129568106312</v>
       </c>
       <c r="W3">
-        <v>-0.1829745596868884</v>
+        <v>-0.1062155782848151</v>
       </c>
       <c r="X3">
-        <v>0.1343347019657854</v>
+        <v>0.2534166811357051</v>
       </c>
       <c r="Y3">
-        <v>-0.3173092616526738</v>
+        <v>-0.3596322594205202</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.3012598137666606</v>
+        <v>-0.2761061946902655</v>
       </c>
       <c r="AB3">
-        <v>0.1343347019657854</v>
+        <v>0.2534166811357051</v>
       </c>
       <c r="AC3">
-        <v>-0.435594515732446</v>
+        <v>-0.5295228758259707</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -752,7 +752,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-27.3</v>
+        <v>-15</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -761,22 +761,22 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.2355478861087144</v>
+        <v>-0.199203187250996</v>
       </c>
       <c r="AK3">
-        <v>-0.1866028708133972</v>
+        <v>-0.09213759213759214</v>
       </c>
       <c r="AL3">
-        <v>0.049</v>
+        <v>0.011</v>
       </c>
       <c r="AM3">
-        <v>0.049</v>
+        <v>-0.05400000000000001</v>
       </c>
       <c r="AO3">
-        <v>-336.734693877551</v>
+        <v>-1418.181818181818</v>
       </c>
       <c r="AQ3">
-        <v>-336.734693877551</v>
+        <v>288.8888888888889</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/british_virgin_islands/british_virgin_islands_drugs_biotechnology.xlsx
@@ -588,7 +588,7 @@
         </is>
       </c>
       <c r="K2">
-        <v>-13.5</v>
+        <v>-113</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,67 +612,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>15</v>
+        <v>3.45</v>
       </c>
       <c r="V2">
-        <v>0.1661129568106312</v>
+        <v>0.09583333333333334</v>
       </c>
       <c r="W2">
-        <v>-0.1062155782848151</v>
+        <v>-0.6334080717488789</v>
       </c>
       <c r="X2">
-        <v>0.2534166811357051</v>
+        <v>0.1427643833599762</v>
       </c>
       <c r="Y2">
-        <v>-0.3596322594205202</v>
+        <v>-0.7761724551088551</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.2761061946902655</v>
+        <v>-0.158465387823186</v>
       </c>
       <c r="AB2">
-        <v>0.2534166811357051</v>
+        <v>0.1420880901063316</v>
       </c>
       <c r="AC2">
-        <v>-0.5295228758259707</v>
+        <v>-0.3005534779295176</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AG2">
-        <v>-15</v>
+        <v>-3.164</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.007881827702144076</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.004250512736676277</v>
       </c>
       <c r="AJ2">
-        <v>-0.199203187250996</v>
+        <v>-0.09635765623096602</v>
       </c>
       <c r="AK2">
-        <v>-0.09213759213759214</v>
+        <v>-0.04956450905445204</v>
       </c>
       <c r="AL2">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="AM2">
-        <v>-0.05400000000000001</v>
+        <v>-0.275</v>
       </c>
       <c r="AO2">
-        <v>-1418.181818181818</v>
+        <v>-1187.5</v>
       </c>
       <c r="AQ2">
-        <v>288.8888888888889</v>
+        <v>69.09090909090909</v>
       </c>
     </row>
     <row r="3">
@@ -692,7 +692,7 @@
         </is>
       </c>
       <c r="K3">
-        <v>-13.5</v>
+        <v>-113</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -716,67 +716,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>15</v>
+        <v>3.45</v>
       </c>
       <c r="V3">
-        <v>0.1661129568106312</v>
+        <v>0.09583333333333334</v>
       </c>
       <c r="W3">
-        <v>-0.1062155782848151</v>
+        <v>-0.6334080717488789</v>
       </c>
       <c r="X3">
-        <v>0.2534166811357051</v>
+        <v>0.1427643833599762</v>
       </c>
       <c r="Y3">
-        <v>-0.3596322594205202</v>
+        <v>-0.7761724551088551</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.2761061946902655</v>
+        <v>-0.158465387823186</v>
       </c>
       <c r="AB3">
-        <v>0.2534166811357051</v>
+        <v>0.1420880901063316</v>
       </c>
       <c r="AC3">
-        <v>-0.5295228758259707</v>
+        <v>-0.3005534779295176</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="AG3">
-        <v>-15</v>
+        <v>-3.164</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.007881827702144076</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.004250512736676277</v>
       </c>
       <c r="AJ3">
-        <v>-0.199203187250996</v>
+        <v>-0.09635765623096602</v>
       </c>
       <c r="AK3">
-        <v>-0.09213759213759214</v>
+        <v>-0.04956450905445204</v>
       </c>
       <c r="AL3">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="AM3">
-        <v>-0.05400000000000001</v>
+        <v>-0.275</v>
       </c>
       <c r="AO3">
-        <v>-1418.181818181818</v>
+        <v>-1187.5</v>
       </c>
       <c r="AQ3">
-        <v>288.8888888888889</v>
+        <v>69.09090909090909</v>
       </c>
     </row>
   </sheetData>
